--- a/static/esempio_paziente_completo_filled_junior.xlsx
+++ b/static/esempio_paziente_completo_filled_junior.xlsx
@@ -5,20 +5,20 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio Base" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Foglio Plus" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Foglio Vita" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Foglio Sport" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Foglio Ageing" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Foglio Junior_intolleranze" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="Foglio Junior_fragilita" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="Foglio Junior_carie" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="Foglio Junior_sindrome_met" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="Foglio Mamma" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="Foglio Condizioni" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="Foglio Base" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Foglio Plus" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Foglio Vita" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Foglio Sport" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Foglio Ageing" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Foglio Junior_intolleranze" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Foglio Junior_fragilita" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Foglio Junior_carie" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Foglio Junior_sindrome_met" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Foglio Mamma" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Foglio Condizioni" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Foglio Base'!$A$2:$H$38</definedName>
@@ -288,7 +288,7 @@
     <t xml:space="preserve">rs762551</t>
   </si>
   <si>
-    <t xml:space="preserve">HLADQA1-B1</t>
+    <t xml:space="preserve">HLA_DQA1-B1</t>
   </si>
   <si>
     <t xml:space="preserve">xxx1</t>
@@ -753,7 +753,7 @@
     <t xml:space="preserve">CONDIZIONI</t>
   </si>
   <si>
-    <t xml:space="preserve">Musulmano, alimenti halal</t>
+    <t xml:space="preserve">Esofagite eosinofila</t>
   </si>
 </sst>
 </file>
@@ -1059,516 +1059,520 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="129">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="justify" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1644,789 +1648,895 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q38"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="7.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="22.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="5.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="18" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="7.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="12.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="15.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="22.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="18.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="22.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="14.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="18" style="2" width="5.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="10" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="D13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="D14" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="D15" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="D17" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="32" t="s">
+      <c r="D18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="31" t="s">
+      <c r="D19" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="32" t="s">
+      <c r="D21" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="17"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="D22" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="n">
+      <c r="D23" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="D24" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="D25" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="17"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="31" t="s">
+      <c r="D26" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="17"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="30" t="s">
+      <c r="D27" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="17"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="32" t="s">
+      <c r="D28" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="30" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="17"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="17"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="n">
+      <c r="D29" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="17"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16"/>
+      <c r="D30" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="17"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="n">
+      <c r="D31" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="17"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="32" t="s">
+      <c r="D32" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="n">
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="17"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="29" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="30" t="s">
+      <c r="C33" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="n">
+      <c r="D33" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="17"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="30" t="s">
+      <c r="C34" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="31" t="s">
+      <c r="D34" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="16"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="n">
+      <c r="F34" s="16"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="37" t="s">
+      <c r="B35" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="38" t="s">
+      <c r="C35" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="16"/>
-    </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="28" t="n">
+      <c r="D35" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="37" t="s">
+      <c r="B36" s="38" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="16"/>
-    </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="n">
+      <c r="D36" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="18"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="37" t="s">
+      <c r="B37" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="38" t="s">
+      <c r="C37" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="40" t="s">
+      <c r="D37" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="18"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="16"/>
-    </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="n">
+      <c r="F37" s="16"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2451,545 +2561,545 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="19.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="39.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="25.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="19" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="14.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="20.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="7.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="14.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="12.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="19.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="22.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="2" width="39.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="2" width="25.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="19" style="2" width="5.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="117" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="117" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="117" t="s">
+      <c r="E5" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="117" t="s">
+      <c r="E6" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="117" t="s">
+      <c r="E7" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="117" t="s">
+      <c r="E8" s="118" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="117" t="s">
+      <c r="E9" s="118" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="117" t="s">
+      <c r="E10" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="117" t="s">
+      <c r="E11" s="118" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="69"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="47" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="D13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="D15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C16" s="30" t="s">
+      <c r="C16" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="49" t="s">
+      <c r="D16" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="50" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="D18" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>216</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="E20" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="D22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="n">
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="31" t="s">
         <v>226</v>
       </c>
-      <c r="D24" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="D24" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="31" t="s">
         <v>228</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="49" t="s">
+      <c r="E25" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="D26" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="D26" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="D27" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="30" t="s">
+      <c r="D27" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="31" t="s">
         <v>234</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="49" t="s">
+      <c r="E28" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="30" t="s">
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="31" t="s">
+      <c r="E29" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="17"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3014,154 +3124,154 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62890625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="18.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="22.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="24.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="20.17"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="118" t="s">
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="119" t="s">
         <v>236</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="118"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="119" t="s">
+      <c r="A2" s="120" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="119"/>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="F2" s="120" t="s">
+      <c r="B2" s="120"/>
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="F2" s="121" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-    </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
+    </row>
+    <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="122" t="s">
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="123" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>12345678</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="121"/>
-      <c r="E4" s="122" t="s">
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>666</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="E5" s="122" t="s">
+      <c r="E5" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="123"/>
-      <c r="H5" s="123"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
-      <c r="E6" s="122" t="s">
+      <c r="E6" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
-      <c r="E7" s="122" t="s">
+      <c r="E7" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
-      <c r="E8" s="122" t="s">
+      <c r="E8" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
-      <c r="E9" s="122" t="s">
+      <c r="E9" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="E10" s="122" t="s">
+      <c r="E10" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="124" t="s">
+      <c r="F10" s="125" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="125"/>
-      <c r="H10" s="125"/>
+      <c r="G10" s="126"/>
+      <c r="H10" s="126"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="E11" s="122" t="s">
+      <c r="E11" s="123" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="124" t="s">
+      <c r="F11" s="125" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="125"/>
-      <c r="H11" s="125"/>
+      <c r="G11" s="126"/>
+      <c r="H11" s="126"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="126" t="s">
+      <c r="E12" s="127" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="127" t="s">
+      <c r="F12" s="128" t="s">
         <v>238</v>
       </c>
-      <c r="G12" s="127"/>
-      <c r="H12" s="127"/>
+      <c r="G12" s="128"/>
+      <c r="H12" s="128"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3179,379 +3289,379 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="15.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="5.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="0" width="23.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="36.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="20" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="10.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="19.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="14.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="15.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="14.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="7.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="2" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="16" style="2" width="23.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="2" width="36.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="20" style="2" width="5.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="15"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="12"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="15"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="15"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="15"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="15"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="15"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="15"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="25"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="26"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="47" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="E14" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="50" t="s">
+      <c r="D15" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="D19" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="50" t="s">
+      <c r="D19" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="52" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="15"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3576,552 +3686,552 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q23"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="18.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="7.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="17.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="2" width="5.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7"/>
+      <c r="Q2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="44"/>
-      <c r="N3" s="18"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="16"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="17"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="16"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="17"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="45"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="16"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="12"/>
+      <c r="Q6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="45"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="17"/>
-      <c r="P7" s="11"/>
-      <c r="Q7" s="16"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="19"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="16"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="17"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="11"/>
-      <c r="Q9" s="16"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="46"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="23"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="26"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="23"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="26"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="47" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="29"/>
-      <c r="O12" s="29"/>
-      <c r="P12" s="29"/>
-      <c r="Q12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="30"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="31" t="s">
+      <c r="D13" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="17"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="46"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="45"/>
-      <c r="N14" s="18"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="19"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="17"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="19"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="17"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="45"/>
-      <c r="N16" s="18"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="19"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="B17" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="34" t="s">
+      <c r="C17" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="32" t="s">
+      <c r="D17" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="45"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="D18" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="17"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="17"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="45"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="17"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="16"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="E19" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="19"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="17"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="45"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="16"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="17"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="45"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="16"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="17"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="32" t="s">
+      <c r="D22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="45"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="15"/>
-      <c r="Q22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="46"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="17"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
-      <c r="C23" s="53"/>
-      <c r="D23" s="53"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
     </row>
@@ -4148,570 +4258,570 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="14.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="15" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="7.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="15.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="12.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="14.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="2" width="22.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="15" style="2" width="5.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="8" customFormat="true" ht="58.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="32" t="s">
+      <c r="D13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="D14" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="D15" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="D16" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="32" t="s">
+      <c r="D16" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D17" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="D17" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="D19" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="32" t="s">
+      <c r="D20" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="D21" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="D22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="n">
+      <c r="D23" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="D24" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="D25" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="32" t="s">
+      <c r="D25" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="D26" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="D26" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="30" t="s">
+      <c r="E27" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="31" t="s">
+      <c r="D28" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="45"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="17"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="57"/>
-      <c r="C29" s="57"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="59"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="59"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="61"/>
-      <c r="C34" s="62"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="64"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="63"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="65"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="61"/>
-      <c r="C35" s="62"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="64"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="63"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="65"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="61"/>
-      <c r="C36" s="62"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="64"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="63"/>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="61"/>
-      <c r="C37" s="62"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="64"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4736,497 +4846,497 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="14" style="0" width="5.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="17.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="12.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="10.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="12.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="13.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="12.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="12.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="13.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="14" style="2" width="5.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-    </row>
-    <row r="2" s="7" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="2" s="8" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="47" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="D13" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="31" t="s">
+      <c r="D14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="17"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="F14" s="16"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="F15" s="16"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="31" t="s">
+      <c r="D16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="E16" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="E17" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="17"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="F18" s="16"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="34" t="s">
+      <c r="C19" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="D19" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="F20" s="16"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="30" t="s">
+      <c r="C21" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="D21" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C22" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="D22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="30" t="s">
+      <c r="C23" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="n">
+      <c r="D23" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="F24" s="16"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="30" t="s">
+      <c r="C25" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="18"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="F25" s="16"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="32" t="s">
+      <c r="E26" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="F26" s="16"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="D27" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="45"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="17"/>
+      <c r="D27" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5251,388 +5361,388 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62890625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="0" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="16.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="6" style="2" width="19.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>12345678</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>666</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="71" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="72" t="n">
+      <c r="A13" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="73" t="s">
+      <c r="B13" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C13" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="0" t="s">
+      <c r="E13" s="76" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72" t="n">
+      <c r="A14" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="50" t="s">
+      <c r="D14" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="n">
+      <c r="A15" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="77" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="49" t="s">
+      <c r="D15" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="n">
+      <c r="A16" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="77" t="s">
         <v>165</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="0" t="s">
+      <c r="E16" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="n">
+      <c r="A17" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="76" t="s">
+      <c r="B17" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="C17" s="76" t="s">
+      <c r="C17" s="77" t="s">
         <v>166</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="0" t="s">
+      <c r="E17" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="72" t="n">
+      <c r="A18" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="77" t="s">
         <v>164</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="77" t="s">
         <v>167</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="0" t="s">
+      <c r="E18" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="n">
+      <c r="A19" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="72" t="n">
+      <c r="A20" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="50" t="s">
+      <c r="D20" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="72" t="n">
+      <c r="A21" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="78" t="s">
         <v>169</v>
       </c>
-      <c r="D21" s="78" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="79" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="0" t="s">
+      <c r="D21" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="E21" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="72" t="n">
+      <c r="A22" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="80" t="s">
+      <c r="B22" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="81" t="s">
+      <c r="D22" s="82" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="82" t="s">
+      <c r="E22" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="83"/>
+      <c r="A23" s="84"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
@@ -5863,576 +5973,576 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J103"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62890625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="16.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="2" width="19.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>12345678</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>666</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="12" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="71" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="72" t="n">
+      <c r="A13" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="75" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="86" t="s">
+      <c r="D13" s="76" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72" t="n">
+      <c r="A14" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="n">
+      <c r="A15" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="30" t="s">
+      <c r="B15" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="31" t="s">
+      <c r="D15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="n">
+      <c r="A16" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="n">
+      <c r="A17" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="D17" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="89" t="s">
+      <c r="D17" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="72" t="n">
+      <c r="A18" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="D18" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="D18" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="n">
+      <c r="A19" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="90" t="s">
+      <c r="B19" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="88" t="s">
+      <c r="E19" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="72" t="n">
+      <c r="A20" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="88" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="87" t="s">
+      <c r="C20" s="88" t="s">
         <v>172</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="89" t="s">
+      <c r="E20" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="72" t="n">
+      <c r="A21" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="88" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="91" t="s">
+      <c r="C21" s="92" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="92" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="E21" s="93" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="72" t="n">
+      <c r="A22" s="73" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="87" t="s">
+      <c r="B22" s="88" t="s">
         <v>175</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="88" t="s">
         <v>176</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="E22" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="72" t="n">
+      <c r="A23" s="73" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="87" t="s">
+      <c r="B23" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="88" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="89" t="s">
+      <c r="D23" s="89" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="72" t="n">
+      <c r="A24" s="73" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="87" t="s">
+      <c r="C24" s="88" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="72" t="n">
+      <c r="A25" s="73" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="91" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="90" t="s">
+      <c r="C25" s="91" t="s">
         <v>178</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="E25" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="72" t="n">
+      <c r="A26" s="73" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="91" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="91" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="88" t="s">
+      <c r="D26" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="89" t="s">
         <v>24</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="72" t="n">
+      <c r="A27" s="73" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="91" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="90" t="s">
+      <c r="C27" s="91" t="s">
         <v>181</v>
       </c>
-      <c r="D27" s="89" t="s">
+      <c r="D27" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="88" t="s">
+      <c r="E27" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="72" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="90" t="s">
+      <c r="A28" s="73" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="91" t="s">
         <v>97</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="91" t="s">
         <v>98</v>
       </c>
-      <c r="D28" s="89" t="s">
+      <c r="D28" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="E28" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="72" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="90" t="s">
+      <c r="A29" s="73" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="91" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="90" t="s">
+      <c r="C29" s="91" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="89" t="s">
+      <c r="D29" s="90" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="88" t="s">
+      <c r="E29" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="72" t="n">
+      <c r="A30" s="73" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="90" t="s">
+      <c r="B30" s="91" t="s">
         <v>184</v>
       </c>
-      <c r="C30" s="90" t="s">
+      <c r="C30" s="91" t="s">
         <v>185</v>
       </c>
-      <c r="D30" s="89" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="D30" s="90" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="89" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="72" t="n">
+      <c r="A31" s="73" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="90" t="s">
+      <c r="B31" s="91" t="s">
         <v>186</v>
       </c>
-      <c r="C31" s="93" t="s">
+      <c r="C31" s="94" t="s">
         <v>187</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E31" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="E31" s="90" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="83"/>
+      <c r="A32" s="84"/>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1"/>
@@ -6663,396 +6773,396 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62890625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="16.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="2" width="19.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>12345678</v>
       </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>666</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="44"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="17"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="65"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="23"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="66"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="24"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="26"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="24"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="71" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="72" t="n">
+      <c r="A13" s="73" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="95" t="s">
         <v>188</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="96" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="96" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="97" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="98" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="72" t="n">
+      <c r="A14" s="73" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="99" t="s">
         <v>188</v>
       </c>
-      <c r="C14" s="99" t="s">
+      <c r="C14" s="100" t="s">
         <v>190</v>
       </c>
-      <c r="D14" s="100" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="72" t="n">
+      <c r="A15" s="73" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="99" t="s">
         <v>188</v>
       </c>
-      <c r="C15" s="99" t="s">
+      <c r="C15" s="100" t="s">
         <v>191</v>
       </c>
-      <c r="D15" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="72" t="n">
+      <c r="A16" s="73" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="98" t="s">
+      <c r="B16" s="99" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="99" t="s">
+      <c r="C16" s="100" t="s">
         <v>193</v>
       </c>
-      <c r="D16" s="100" t="s">
+      <c r="D16" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="101" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="E16" s="102" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="72" t="n">
+      <c r="A17" s="73" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="99" t="s">
         <v>192</v>
       </c>
-      <c r="C17" s="99" t="s">
+      <c r="C17" s="100" t="s">
         <v>194</v>
       </c>
-      <c r="D17" s="100" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="72" t="n">
+      <c r="A18" s="73" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="99" t="s">
         <v>195</v>
       </c>
-      <c r="C18" s="99" t="s">
+      <c r="C18" s="100" t="s">
         <v>196</v>
       </c>
-      <c r="D18" s="101" t="s">
+      <c r="D18" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="100" t="s">
+      <c r="E18" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="72" t="n">
+      <c r="A19" s="73" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="100" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="101" t="s">
+      <c r="D19" s="102" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="100" t="s">
+      <c r="E19" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="72" t="n">
+      <c r="A20" s="73" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="C20" s="99" t="s">
+      <c r="C20" s="100" t="s">
         <v>199</v>
       </c>
-      <c r="D20" s="101" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="100" t="s">
+      <c r="D20" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="72" t="n">
+      <c r="A21" s="73" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="98" t="s">
+      <c r="B21" s="99" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="99" t="s">
+      <c r="C21" s="100" t="s">
         <v>200</v>
       </c>
-      <c r="D21" s="100" t="s">
+      <c r="D21" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="E21" s="101" t="s">
+      <c r="E21" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="102" t="n">
+      <c r="A22" s="103" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="104" t="s">
         <v>197</v>
       </c>
-      <c r="C22" s="104" t="s">
+      <c r="C22" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="D22" s="105" t="s">
+      <c r="D22" s="106" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="106" t="s">
+      <c r="E22" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="83"/>
+      <c r="A23" s="84"/>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
@@ -7283,811 +7393,811 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J114"/>
-  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.62890625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="21.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="0" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="16.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="21.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="17.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="7" style="2" width="19.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="43" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>12345678</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="66"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="43" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="12" t="n">
         <v>666</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="66"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="14"/>
     </row>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="66"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="66"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>158</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="66"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="G10" s="20"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" s="70" t="s">
         <v>160</v>
       </c>
-      <c r="G11" s="20"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="71" t="s">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="84"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+      <c r="A13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="107" t="s">
+      <c r="B13" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="107" t="s">
+      <c r="C13" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+      <c r="A14" s="29" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="107" t="s">
+      <c r="B14" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="107" t="s">
+      <c r="C14" s="108" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="n">
+      <c r="A15" s="29" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="107" t="s">
+      <c r="B15" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="107" t="s">
+      <c r="C15" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+      <c r="A16" s="29" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="110" t="s">
+      <c r="C16" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="108" t="s">
+      <c r="D16" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="109" t="s">
+      <c r="E16" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+      <c r="A17" s="29" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="107" t="s">
+      <c r="C17" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="108" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="109" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+      <c r="A18" s="29" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="107" t="s">
+      <c r="C18" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="109" t="s">
+      <c r="D18" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+      <c r="A19" s="29" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="111" t="s">
+      <c r="B19" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="C19" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="108" t="s">
+      <c r="D19" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="28" t="n">
+      <c r="A20" s="29" t="n">
         <v>8</v>
       </c>
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="98" t="s">
+      <c r="C20" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="109" t="s">
+      <c r="D20" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="108" t="s">
+      <c r="E20" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="28" t="n">
+      <c r="A21" s="29" t="n">
         <v>9</v>
       </c>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="107" t="s">
+      <c r="C21" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="109" t="s">
+      <c r="D21" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="28" t="n">
+      <c r="A22" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="107" t="s">
+      <c r="C22" s="108" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28" t="n">
+      <c r="A23" s="29" t="n">
         <v>11</v>
       </c>
-      <c r="B23" s="107" t="s">
+      <c r="B23" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="D23" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="28" t="n">
+      <c r="A24" s="29" t="n">
         <v>12</v>
       </c>
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="107" t="s">
+      <c r="C24" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="28" t="n">
+      <c r="A25" s="29" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="107" t="s">
+      <c r="C25" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="D25" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="28" t="n">
+      <c r="A26" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="108" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="107" t="s">
+      <c r="C26" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="D26" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="108" t="s">
+      <c r="D26" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="28" t="n">
+      <c r="A27" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="107" t="s">
+      <c r="C27" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="D27" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="28" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="107" t="s">
+      <c r="A28" s="29" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="107" t="s">
+      <c r="C28" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="109" t="s">
+      <c r="D28" s="110" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="108" t="s">
+      <c r="E28" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="28" t="n">
-        <v>17</v>
-      </c>
-      <c r="B29" s="107" t="s">
+      <c r="A29" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="107" t="s">
+      <c r="C29" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="D29" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E29" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28" t="n">
+      <c r="A30" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="B30" s="110" t="s">
+      <c r="B30" s="111" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="110" t="s">
+      <c r="C30" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="D30" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="28" t="n">
+      <c r="A31" s="29" t="n">
         <v>19</v>
       </c>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="108" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="112" t="s">
+      <c r="C31" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="D31" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E31" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28" t="n">
+      <c r="A32" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="108" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="109" t="s">
+      <c r="D32" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="108" t="s">
+      <c r="E32" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="28" t="n">
+      <c r="A33" s="29" t="n">
         <v>21</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="C33" s="107" t="s">
+      <c r="C33" s="108" t="s">
         <v>56</v>
       </c>
-      <c r="D33" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="D33" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="28" t="n">
+      <c r="A34" s="29" t="n">
         <v>22</v>
       </c>
-      <c r="B34" s="107" t="s">
+      <c r="B34" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="107" t="s">
+      <c r="C34" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="E34" s="108" t="s">
+      <c r="D34" s="110" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="28" t="n">
+      <c r="A35" s="29" t="n">
         <v>23</v>
       </c>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="108" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="107" t="s">
+      <c r="C35" s="108" t="s">
         <v>60</v>
       </c>
-      <c r="D35" s="113" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="2" t="s">
+      <c r="D35" s="114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="28" t="n">
+      <c r="A36" s="29" t="n">
         <v>24</v>
       </c>
-      <c r="B36" s="107" t="s">
+      <c r="B36" s="108" t="s">
         <v>61</v>
       </c>
-      <c r="C36" s="107" t="s">
+      <c r="C36" s="108" t="s">
         <v>62</v>
       </c>
-      <c r="D36" s="113" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="2" t="s">
+      <c r="D36" s="114" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28" t="n">
+      <c r="A37" s="29" t="n">
         <v>25</v>
       </c>
-      <c r="B37" s="107" t="s">
+      <c r="B37" s="108" t="s">
         <v>63</v>
       </c>
-      <c r="C37" s="107" t="s">
+      <c r="C37" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="D37" s="109" t="s">
-        <v>16</v>
-      </c>
-      <c r="E37" s="108" t="s">
+      <c r="D37" s="110" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28" t="n">
+      <c r="A38" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="107" t="s">
+      <c r="C38" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="D38" s="109" t="s">
+      <c r="D38" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="108" t="s">
+      <c r="E38" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="28" t="n">
+      <c r="A39" s="29" t="n">
         <v>27</v>
       </c>
-      <c r="B39" s="99" t="s">
+      <c r="B39" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="98" t="s">
+      <c r="C39" s="99" t="s">
         <v>202</v>
       </c>
-      <c r="D39" s="108" t="s">
+      <c r="D39" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="109" t="s">
+      <c r="E39" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28" t="n">
+      <c r="A40" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="B40" s="99" t="s">
+      <c r="B40" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="98" t="s">
+      <c r="C40" s="99" t="s">
         <v>203</v>
       </c>
-      <c r="D40" s="108" t="s">
-        <v>16</v>
-      </c>
-      <c r="E40" s="109" t="s">
+      <c r="D40" s="109" t="s">
+        <v>16</v>
+      </c>
+      <c r="E40" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="3" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="28" t="n">
+      <c r="A41" s="29" t="n">
         <v>29</v>
       </c>
-      <c r="B41" s="99" t="s">
+      <c r="B41" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="98" t="s">
+      <c r="C41" s="99" t="s">
         <v>204</v>
       </c>
-      <c r="D41" s="108" t="s">
-        <v>17</v>
-      </c>
-      <c r="E41" s="109" t="s">
+      <c r="D41" s="109" t="s">
+        <v>17</v>
+      </c>
+      <c r="E41" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="28" t="n">
+      <c r="A42" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="B42" s="98" t="s">
+      <c r="B42" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="98" t="s">
+      <c r="C42" s="99" t="s">
         <v>205</v>
       </c>
-      <c r="D42" s="108" t="s">
+      <c r="D42" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="109" t="s">
+      <c r="E42" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="102" t="n">
+      <c r="A43" s="103" t="n">
         <v>31</v>
       </c>
-      <c r="B43" s="114" t="s">
+      <c r="B43" s="115" t="s">
         <v>206</v>
       </c>
-      <c r="C43" s="114" t="s">
+      <c r="C43" s="115" t="s">
         <v>207</v>
       </c>
-      <c r="D43" s="115" t="s">
+      <c r="D43" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="116" t="s">
+      <c r="E43" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="3" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8320,8 +8430,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Normale"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>